--- a/library/connectors.xlsx
+++ b/library/connectors.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E574B665-8311-44D4-9382-BBE165C7E2B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6E781A4-C258-4694-B480-38E8FF5363E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="206">
   <si>
     <t>Part Number</t>
   </si>
@@ -645,6 +645,15 @@
   </si>
   <si>
     <t>con-ru-f-1_empty</t>
+  </si>
+  <si>
+    <t>DG350-3.5-02P-14</t>
+  </si>
+  <si>
+    <t>Degson Electronics</t>
+  </si>
+  <si>
+    <t>con-ru-f-2</t>
   </si>
 </sst>
 </file>
@@ -835,13 +844,14 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Accent 1 1" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1300,7 +1310,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.28515625" style="1" customWidth="1"/>
@@ -2153,6 +2163,26 @@
       </c>
       <c r="F42" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>203</v>
+      </c>
+      <c r="B43" t="s">
+        <v>203</v>
+      </c>
+      <c r="C43" t="s">
+        <v>203</v>
+      </c>
+      <c r="D43" t="s">
+        <v>205</v>
+      </c>
+      <c r="E43" t="s">
+        <v>203</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>

--- a/library/connectors.xlsx
+++ b/library/connectors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6E781A4-C258-4694-B480-38E8FF5363E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE3E761-DC78-4972-B729-A3CC8726BED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Connectors" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="210">
   <si>
     <t>Part Number</t>
   </si>
@@ -654,6 +654,18 @@
   </si>
   <si>
     <t>con-ru-f-2</t>
+  </si>
+  <si>
+    <t>PAD200x150_HOLE</t>
+  </si>
+  <si>
+    <t>Hole 2mm x 1.5 mm</t>
+  </si>
+  <si>
+    <t>PAD260x100_SMD_HOLE</t>
+  </si>
+  <si>
+    <t>Pad_Hole 2.6mm x 1 mm</t>
   </si>
 </sst>
 </file>
@@ -844,14 +856,13 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Accent 1 1" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2181,7 +2192,7 @@
       <c r="E43" t="s">
         <v>203</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" t="s">
         <v>204</v>
       </c>
     </row>
@@ -3020,7 +3031,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3133,6 +3144,28 @@
         <v>192</v>
       </c>
     </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>207</v>
+      </c>
+      <c r="D9" t="s">
+        <v>183</v>
+      </c>
+      <c r="E9" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>209</v>
+      </c>
+      <c r="D10" t="s">
+        <v>183</v>
+      </c>
+      <c r="E10" t="s">
+        <v>208</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.51181102362204722" footer="0.51181102362204722"/>

--- a/library/connectors.xlsx
+++ b/library/connectors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE3E761-DC78-4972-B729-A3CC8726BED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC2094C-B379-4E64-B42D-BAEB17AEFB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Connectors" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="213">
   <si>
     <t>Part Number</t>
   </si>
@@ -666,6 +666,15 @@
   </si>
   <si>
     <t>Pad_Hole 2.6mm x 1 mm</t>
+  </si>
+  <si>
+    <t>226990-1</t>
+  </si>
+  <si>
+    <t>901-10512-3</t>
+  </si>
+  <si>
+    <t>Amphenol</t>
   </si>
 </sst>
 </file>
@@ -856,13 +865,14 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Accent 1 1" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1321,7 +1331,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.28515625" style="1" customWidth="1"/>
@@ -2194,6 +2204,46 @@
       </c>
       <c r="F43" t="s">
         <v>204</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B44" t="s">
+        <v>210</v>
+      </c>
+      <c r="C44" t="s">
+        <v>210</v>
+      </c>
+      <c r="D44" t="s">
+        <v>210</v>
+      </c>
+      <c r="E44">
+        <v>2269901</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B45" t="s">
+        <v>211</v>
+      </c>
+      <c r="C45" t="s">
+        <v>211</v>
+      </c>
+      <c r="D45" t="s">
+        <v>211</v>
+      </c>
+      <c r="E45" t="s">
+        <v>211</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>212</v>
       </c>
     </row>
   </sheetData>

--- a/library/connectors.xlsx
+++ b/library/connectors.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC2094C-B379-4E64-B42D-BAEB17AEFB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B73F4E68-3E97-45A5-B694-6A9E4B1E8EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="215">
   <si>
     <t>Part Number</t>
   </si>
@@ -675,6 +675,12 @@
   </si>
   <si>
     <t>Amphenol</t>
+  </si>
+  <si>
+    <t>50A-15BX</t>
+  </si>
+  <si>
+    <t>Scondar</t>
   </si>
 </sst>
 </file>
@@ -865,14 +871,13 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Accent 1 1" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1331,7 +1336,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.28515625" style="1" customWidth="1"/>
@@ -2222,7 +2227,7 @@
       <c r="E44">
         <v>2269901</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" t="s">
         <v>197</v>
       </c>
     </row>
@@ -2242,8 +2247,28 @@
       <c r="E45" t="s">
         <v>211</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F45" t="s">
         <v>212</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>213</v>
+      </c>
+      <c r="B46" t="s">
+        <v>213</v>
+      </c>
+      <c r="C46" t="s">
+        <v>213</v>
+      </c>
+      <c r="D46" t="s">
+        <v>113</v>
+      </c>
+      <c r="E46" t="s">
+        <v>213</v>
+      </c>
+      <c r="F46" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/library/connectors.xlsx
+++ b/library/connectors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B73F4E68-3E97-45A5-B694-6A9E4B1E8EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA15EDF-8833-48AB-B3E1-05A760C8EAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="217">
   <si>
     <t>Part Number</t>
   </si>
@@ -681,6 +681,12 @@
   </si>
   <si>
     <t>Scondar</t>
+  </si>
+  <si>
+    <t>con-ru-m-36</t>
+  </si>
+  <si>
+    <t>DS1079-M36</t>
   </si>
 </sst>
 </file>
@@ -1336,7 +1342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.28515625" style="1" customWidth="1"/>
@@ -2269,6 +2275,26 @@
       </c>
       <c r="F46" t="s">
         <v>214</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>216</v>
+      </c>
+      <c r="B47" t="s">
+        <v>216</v>
+      </c>
+      <c r="C47" t="s">
+        <v>216</v>
+      </c>
+      <c r="D47" t="s">
+        <v>215</v>
+      </c>
+      <c r="E47" t="s">
+        <v>216</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/library/connectors.xlsx
+++ b/library/connectors.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA15EDF-8833-48AB-B3E1-05A760C8EAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8043A1CB-AB81-4AFA-A46F-42EEC53A56F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="220">
   <si>
     <t>Part Number</t>
   </si>
@@ -687,6 +687,15 @@
   </si>
   <si>
     <t>DS1079-M36</t>
+  </si>
+  <si>
+    <t>con-ru-m-40</t>
+  </si>
+  <si>
+    <t>DS1031-06-2X40-P8BV41-3A</t>
+  </si>
+  <si>
+    <t>PLL-40</t>
   </si>
 </sst>
 </file>
@@ -1342,7 +1351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.28515625" style="1" customWidth="1"/>
@@ -2296,6 +2305,29 @@
       <c r="F47" s="1" t="s">
         <v>47</v>
       </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>218</v>
+      </c>
+      <c r="B48" t="s">
+        <v>218</v>
+      </c>
+      <c r="C48" t="s">
+        <v>218</v>
+      </c>
+      <c r="D48" t="s">
+        <v>217</v>
+      </c>
+      <c r="E48" t="s">
+        <v>219</v>
+      </c>
+      <c r="F48" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A49"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>

--- a/library/connectors.xlsx
+++ b/library/connectors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8043A1CB-AB81-4AFA-A46F-42EEC53A56F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD4926A-36CC-4A0A-BF7B-57B8BD15BC04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Connectors" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="226">
   <si>
     <t>Part Number</t>
   </si>
@@ -696,6 +696,24 @@
   </si>
   <si>
     <t>PLL-40</t>
+  </si>
+  <si>
+    <t>РПС1-37Ш</t>
+  </si>
+  <si>
+    <t>АСЛР.434410.022ТУ</t>
+  </si>
+  <si>
+    <t>РПС1-37Г</t>
+  </si>
+  <si>
+    <t>con-ru-m-37</t>
+  </si>
+  <si>
+    <t>con-ru-f-37</t>
+  </si>
+  <si>
+    <t>РПС1-15Г</t>
   </si>
 </sst>
 </file>
@@ -2743,7 +2761,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.5703125" customWidth="1"/>
@@ -3152,6 +3170,66 @@
       </c>
       <c r="F20" t="s">
         <v>176</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>220</v>
+      </c>
+      <c r="B21" t="s">
+        <v>220</v>
+      </c>
+      <c r="C21" t="s">
+        <v>220</v>
+      </c>
+      <c r="D21" t="s">
+        <v>223</v>
+      </c>
+      <c r="E21" t="s">
+        <v>220</v>
+      </c>
+      <c r="F21" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>222</v>
+      </c>
+      <c r="B22" t="s">
+        <v>222</v>
+      </c>
+      <c r="C22" t="s">
+        <v>222</v>
+      </c>
+      <c r="D22" t="s">
+        <v>224</v>
+      </c>
+      <c r="E22" t="s">
+        <v>222</v>
+      </c>
+      <c r="F22" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>225</v>
+      </c>
+      <c r="B23" t="s">
+        <v>225</v>
+      </c>
+      <c r="C23" t="s">
+        <v>225</v>
+      </c>
+      <c r="D23" t="s">
+        <v>113</v>
+      </c>
+      <c r="E23" t="s">
+        <v>225</v>
+      </c>
+      <c r="F23" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/library/connectors.xlsx
+++ b/library/connectors.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD4926A-36CC-4A0A-BF7B-57B8BD15BC04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CC93F9-475B-465F-97CB-E730958DFEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="228">
   <si>
     <t>Part Number</t>
   </si>
@@ -714,6 +714,12 @@
   </si>
   <si>
     <t>РПС1-15Г</t>
+  </si>
+  <si>
+    <t>РПС1-37Г_TH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РПС1-37Ш </t>
   </si>
 </sst>
 </file>
@@ -2761,7 +2767,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.5703125" customWidth="1"/>
@@ -3174,7 +3180,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B21" t="s">
         <v>220</v>
@@ -3229,6 +3235,26 @@
         <v>225</v>
       </c>
       <c r="F23" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>220</v>
+      </c>
+      <c r="B24" t="s">
+        <v>220</v>
+      </c>
+      <c r="C24" t="s">
+        <v>220</v>
+      </c>
+      <c r="D24" t="s">
+        <v>223</v>
+      </c>
+      <c r="E24" t="s">
+        <v>226</v>
+      </c>
+      <c r="F24" t="s">
         <v>221</v>
       </c>
     </row>

--- a/library/connectors.xlsx
+++ b/library/connectors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CC93F9-475B-465F-97CB-E730958DFEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{302258EE-1AE1-4F03-9ED5-E048529B1706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="229">
   <si>
     <t>Part Number</t>
   </si>
@@ -720,6 +720,9 @@
   </si>
   <si>
     <t xml:space="preserve">РПС1-37Ш </t>
+  </si>
+  <si>
+    <t xml:space="preserve">РПС1-37Г </t>
   </si>
 </sst>
 </file>
@@ -3240,13 +3243,13 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C24" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D24" t="s">
         <v>223</v>

--- a/library/connectors.xlsx
+++ b/library/connectors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{302258EE-1AE1-4F03-9ED5-E048529B1706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26259E07-AA2B-483C-A858-785E4EF72BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="230">
   <si>
     <t>Part Number</t>
   </si>
@@ -723,6 +723,9 @@
   </si>
   <si>
     <t xml:space="preserve">РПС1-37Г </t>
+  </si>
+  <si>
+    <t>РПС1-37Г.</t>
   </si>
 </sst>
 </file>
@@ -3203,7 +3206,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s">
         <v>222</v>
@@ -3243,13 +3246,13 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>222</v>
+      </c>
+      <c r="B24" t="s">
         <v>228</v>
       </c>
-      <c r="B24" t="s">
-        <v>222</v>
-      </c>
       <c r="C24" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D24" t="s">
         <v>223</v>

--- a/library/connectors.xlsx
+++ b/library/connectors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26259E07-AA2B-483C-A858-785E4EF72BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69ABA589-97D0-4D42-8EB5-0EB67AE87CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="230">
   <si>
     <t>Part Number</t>
   </si>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">РПС1-37Г </t>
   </si>
   <si>
-    <t>РПС1-37Г.</t>
+    <t>Footprint Ref 2</t>
   </si>
 </sst>
 </file>
@@ -2773,18 +2773,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.5703125" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="24.7109375" customWidth="1"/>
-    <col min="4" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="39.140625" customWidth="1"/>
-    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="4" max="6" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="39.140625" customWidth="1"/>
+    <col min="8" max="8" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2801,10 +2801,13 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>124</v>
       </c>
@@ -2820,11 +2823,11 @@
       <c r="E2" t="s">
         <v>126</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>128</v>
       </c>
@@ -2840,11 +2843,11 @@
       <c r="E3" t="s">
         <v>130</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>131</v>
       </c>
@@ -2860,11 +2863,11 @@
       <c r="E4" t="s">
         <v>133</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>134</v>
       </c>
@@ -2880,11 +2883,11 @@
       <c r="E5" t="s">
         <v>135</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>137</v>
       </c>
@@ -2900,11 +2903,11 @@
       <c r="E6" t="s">
         <v>139</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>141</v>
       </c>
@@ -2920,11 +2923,11 @@
       <c r="E7" t="s">
         <v>142</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>144</v>
       </c>
@@ -2940,11 +2943,11 @@
       <c r="E8" t="s">
         <v>145</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>146</v>
       </c>
@@ -2960,11 +2963,11 @@
       <c r="E9" t="s">
         <v>147</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>148</v>
       </c>
@@ -2980,11 +2983,11 @@
       <c r="E10" t="s">
         <v>72</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>150</v>
       </c>
@@ -3000,11 +3003,11 @@
       <c r="E11" t="s">
         <v>151</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>153</v>
       </c>
@@ -3020,11 +3023,11 @@
       <c r="E12" t="s">
         <v>155</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>156</v>
       </c>
@@ -3040,11 +3043,11 @@
       <c r="E13" t="s">
         <v>158</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>159</v>
       </c>
@@ -3060,11 +3063,11 @@
       <c r="E14" t="s">
         <v>160</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>161</v>
       </c>
@@ -3080,11 +3083,11 @@
       <c r="E15" t="s">
         <v>163</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>164</v>
       </c>
@@ -3100,11 +3103,11 @@
       <c r="E16" t="s">
         <v>165</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>166</v>
       </c>
@@ -3120,11 +3123,11 @@
       <c r="E17" t="s">
         <v>168</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>169</v>
       </c>
@@ -3140,11 +3143,11 @@
       <c r="E18" t="s">
         <v>171</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>172</v>
       </c>
@@ -3160,11 +3163,11 @@
       <c r="E19" t="s">
         <v>61</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>174</v>
       </c>
@@ -3180,11 +3183,11 @@
       <c r="E20" t="s">
         <v>174</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>227</v>
       </c>
@@ -3200,13 +3203,13 @@
       <c r="E21" t="s">
         <v>220</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s">
         <v>222</v>
@@ -3221,10 +3224,13 @@
         <v>222</v>
       </c>
       <c r="F22" t="s">
+        <v>226</v>
+      </c>
+      <c r="G22" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>225</v>
       </c>
@@ -3240,11 +3246,11 @@
       <c r="E23" t="s">
         <v>225</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>222</v>
       </c>
@@ -3260,7 +3266,7 @@
       <c r="E24" t="s">
         <v>226</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>221</v>
       </c>
     </row>

--- a/library/connectors.xlsx
+++ b/library/connectors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69ABA589-97D0-4D42-8EB5-0EB67AE87CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0D2D03-56FC-4925-BD63-76BE43FE5B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Connectors" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="232">
   <si>
     <t>Part Number</t>
   </si>
@@ -726,6 +726,12 @@
   </si>
   <si>
     <t>Footprint Ref 2</t>
+  </si>
+  <si>
+    <t>PAD200x150</t>
+  </si>
+  <si>
+    <t>Pad 2 mm x 1.5 mm</t>
   </si>
 </sst>
 </file>
@@ -3280,7 +3286,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3415,6 +3421,17 @@
         <v>208</v>
       </c>
     </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>231</v>
+      </c>
+      <c r="D11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E11" t="s">
+        <v>230</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.51181102362204722" footer="0.51181102362204722"/>

--- a/library/connectors.xlsx
+++ b/library/connectors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0D2D03-56FC-4925-BD63-76BE43FE5B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD12376-EA8A-44C9-8707-06D4281376D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Connectors" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="236">
   <si>
     <t>Part Number</t>
   </si>
@@ -732,6 +732,18 @@
   </si>
   <si>
     <t>Pad 2 mm x 1.5 mm</t>
+  </si>
+  <si>
+    <t>DRB-37FA</t>
+  </si>
+  <si>
+    <t>USBB-1J</t>
+  </si>
+  <si>
+    <t>USBB-1J (DS1099-W)</t>
+  </si>
+  <si>
+    <t>DS1099-W</t>
   </si>
 </sst>
 </file>
@@ -1387,7 +1399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.28515625" style="1" customWidth="1"/>
@@ -2338,7 +2350,7 @@
       <c r="E47" t="s">
         <v>216</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" t="s">
         <v>47</v>
       </c>
     </row>
@@ -2362,8 +2374,40 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A49"/>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>234</v>
+      </c>
+      <c r="B49" t="s">
+        <v>235</v>
+      </c>
+      <c r="C49" t="s">
+        <v>235</v>
+      </c>
+      <c r="D49" t="s">
+        <v>196</v>
+      </c>
+      <c r="E49" t="s">
+        <v>233</v>
+      </c>
+      <c r="F49" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A54"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
@@ -2378,7 +2422,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="20.7109375" customWidth="1"/>
@@ -2766,6 +2810,26 @@
         <v>122</v>
       </c>
       <c r="F19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>232</v>
+      </c>
+      <c r="B20" t="s">
+        <v>232</v>
+      </c>
+      <c r="C20" t="s">
+        <v>232</v>
+      </c>
+      <c r="D20" t="s">
+        <v>224</v>
+      </c>
+      <c r="E20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F20" t="s">
         <v>47</v>
       </c>
     </row>

--- a/library/connectors.xlsx
+++ b/library/connectors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/garou/Documents/work/elem_altium_db2/library/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD12376-EA8A-44C9-8707-06D4281376D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C0EC87-C2BE-4F4D-8904-900BEE6927F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Connectors" sheetId="1" r:id="rId1"/>
@@ -943,6 +943,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="19">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Accent 1 1" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Accent 2 1" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Accent 3 1" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -961,7 +962,6 @@
     <cellStyle name="Status 1" xfId="16" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
     <cellStyle name="Text 1" xfId="17" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
     <cellStyle name="Warning 1" xfId="18" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1400,20 +1400,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K54"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="35.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" customWidth="1"/>
-    <col min="4" max="4" width="24.5703125" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="21.140625" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.83203125" style="1" customWidth="1"/>
+    <col min="2" max="6" width="25.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="8.42578125" customWidth="1"/>
+    <col min="9" max="9" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" ht="14.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="1" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1438,7 +1434,7 @@
       <c r="J1"/>
       <c r="K1"/>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" ht="14.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" s="1" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>202</v>
       </c>
@@ -1455,7 +1451,7 @@
       <c r="J2"/>
       <c r="K2"/>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1480,7 +1476,7 @@
       <c r="J3"/>
       <c r="K3"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1500,7 +1496,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1520,7 +1516,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1540,7 +1536,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -1560,7 +1556,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -1577,7 +1573,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -1594,7 +1590,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1614,7 +1610,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
@@ -1634,7 +1630,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
@@ -1654,7 +1650,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
@@ -1674,7 +1670,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
@@ -1694,7 +1690,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>39</v>
       </c>
@@ -1714,7 +1710,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="14" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
         <v>41</v>
       </c>
@@ -1734,7 +1730,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
         <v>45</v>
       </c>
@@ -1754,7 +1750,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
         <v>48</v>
       </c>
@@ -1774,7 +1770,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
         <v>51</v>
       </c>
@@ -1794,7 +1790,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
         <v>53</v>
       </c>
@@ -1814,7 +1810,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>55</v>
       </c>
@@ -1834,7 +1830,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>57</v>
       </c>
@@ -1854,7 +1850,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>59</v>
       </c>
@@ -1874,7 +1870,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
         <v>62</v>
       </c>
@@ -1894,7 +1890,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
         <v>66</v>
       </c>
@@ -1914,7 +1910,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>68</v>
       </c>
@@ -1934,7 +1930,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>69</v>
       </c>
@@ -1954,7 +1950,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>70</v>
       </c>
@@ -1974,7 +1970,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>72</v>
       </c>
@@ -1994,7 +1990,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>74</v>
       </c>
@@ -2014,7 +2010,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>77</v>
       </c>
@@ -2034,7 +2030,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
         <v>78</v>
       </c>
@@ -2054,7 +2050,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
         <v>79</v>
       </c>
@@ -2074,7 +2070,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
         <v>81</v>
       </c>
@@ -2094,7 +2090,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
         <v>83</v>
       </c>
@@ -2114,7 +2110,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
         <v>86</v>
       </c>
@@ -2134,7 +2130,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>89</v>
       </c>
@@ -2154,7 +2150,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>91</v>
       </c>
@@ -2174,7 +2170,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
         <v>193</v>
       </c>
@@ -2194,7 +2190,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A40" t="s">
         <v>195</v>
       </c>
@@ -2214,7 +2210,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A41" t="s">
         <v>198</v>
       </c>
@@ -2234,7 +2230,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A42" t="s">
         <v>200</v>
       </c>
@@ -2254,7 +2250,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A43" t="s">
         <v>203</v>
       </c>
@@ -2274,7 +2270,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
         <v>210</v>
       </c>
@@ -2294,7 +2290,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
         <v>211</v>
       </c>
@@ -2314,7 +2310,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A46" t="s">
         <v>213</v>
       </c>
@@ -2334,7 +2330,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A47" t="s">
         <v>216</v>
       </c>
@@ -2354,7 +2350,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A48" t="s">
         <v>218</v>
       </c>
@@ -2374,7 +2370,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
         <v>234</v>
       </c>
@@ -2394,19 +2390,19 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A50"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A51"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A52"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A53"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A54"/>
     </row>
   </sheetData>
@@ -2423,12 +2419,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="6" width="20.7109375" customWidth="1"/>
+    <col min="1" max="6" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" ht="14.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="1" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2453,7 +2449,7 @@
       <c r="J1"/>
       <c r="K1"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>93</v>
       </c>
@@ -2473,7 +2469,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>95</v>
       </c>
@@ -2493,7 +2489,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>97</v>
       </c>
@@ -2513,7 +2509,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>99</v>
       </c>
@@ -2533,7 +2529,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>101</v>
       </c>
@@ -2553,7 +2549,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>102</v>
       </c>
@@ -2573,7 +2569,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>103</v>
       </c>
@@ -2593,7 +2589,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>104</v>
       </c>
@@ -2613,7 +2609,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>106</v>
       </c>
@@ -2633,7 +2629,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>107</v>
       </c>
@@ -2653,7 +2649,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>109</v>
       </c>
@@ -2673,7 +2669,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>112</v>
       </c>
@@ -2693,7 +2689,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>114</v>
       </c>
@@ -2713,7 +2709,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>116</v>
       </c>
@@ -2733,7 +2729,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>118</v>
       </c>
@@ -2753,7 +2749,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>120</v>
       </c>
@@ -2773,7 +2769,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>121</v>
       </c>
@@ -2793,7 +2789,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>122</v>
       </c>
@@ -2813,7 +2809,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>232</v>
       </c>
@@ -2844,17 +2840,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="30.5703125" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" customWidth="1"/>
-    <col min="4" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="39.140625" customWidth="1"/>
+    <col min="1" max="6" width="25.83203125" customWidth="1"/>
+    <col min="7" max="7" width="39.1640625" customWidth="1"/>
     <col min="8" max="8" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2877,7 +2870,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>124</v>
       </c>
@@ -2897,7 +2890,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>128</v>
       </c>
@@ -2917,7 +2910,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>131</v>
       </c>
@@ -2937,7 +2930,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>134</v>
       </c>
@@ -2957,7 +2950,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>137</v>
       </c>
@@ -2977,7 +2970,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>141</v>
       </c>
@@ -2997,7 +2990,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>144</v>
       </c>
@@ -3017,7 +3010,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>146</v>
       </c>
@@ -3037,7 +3030,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>148</v>
       </c>
@@ -3057,7 +3050,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>150</v>
       </c>
@@ -3077,7 +3070,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>153</v>
       </c>
@@ -3097,7 +3090,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>156</v>
       </c>
@@ -3117,7 +3110,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>159</v>
       </c>
@@ -3137,7 +3130,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>161</v>
       </c>
@@ -3157,7 +3150,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>164</v>
       </c>
@@ -3177,7 +3170,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>166</v>
       </c>
@@ -3197,7 +3190,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>169</v>
       </c>
@@ -3217,7 +3210,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>172</v>
       </c>
@@ -3237,7 +3230,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>174</v>
       </c>
@@ -3257,7 +3250,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>227</v>
       </c>
@@ -3277,7 +3270,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>222</v>
       </c>
@@ -3300,7 +3293,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>225</v>
       </c>
@@ -3320,7 +3313,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>222</v>
       </c>
@@ -3351,17 +3344,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="27.7109375" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" customWidth="1"/>
-    <col min="5" max="5" width="24.42578125" customWidth="1"/>
-    <col min="6" max="6" width="23" customWidth="1"/>
+    <col min="1" max="6" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" ht="14.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="1" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3386,7 +3374,7 @@
       <c r="J1"/>
       <c r="K1"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>177</v>
       </c>
@@ -3397,7 +3385,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>180</v>
       </c>
@@ -3408,7 +3396,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>182</v>
       </c>
@@ -3419,7 +3407,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>185</v>
       </c>
@@ -3430,7 +3418,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>187</v>
       </c>
@@ -3441,7 +3429,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>189</v>
       </c>
@@ -3452,7 +3440,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>191</v>
       </c>
@@ -3463,7 +3451,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>207</v>
       </c>
@@ -3474,7 +3462,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>209</v>
       </c>
@@ -3485,7 +3473,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>231</v>
       </c>

--- a/library/connectors.xlsx
+++ b/library/connectors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/garou/Documents/work/elem_altium_db2/library/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C0EC87-C2BE-4F4D-8904-900BEE6927F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE0CE03B-56ED-4390-B28B-163BD22261F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Connectors" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="238">
   <si>
     <t>Part Number</t>
   </si>
@@ -744,6 +744,12 @@
   </si>
   <si>
     <t>DS1099-W</t>
+  </si>
+  <si>
+    <t>PLD-10</t>
+  </si>
+  <si>
+    <t>DS1021-2X5SF11-B</t>
   </si>
 </sst>
 </file>
@@ -943,7 +949,6 @@
     </xf>
   </cellXfs>
   <cellStyles count="19">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Accent 1 1" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Accent 2 1" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Accent 3 1" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -962,6 +967,7 @@
     <cellStyle name="Status 1" xfId="16" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
     <cellStyle name="Text 1" xfId="17" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
     <cellStyle name="Warning 1" xfId="18" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1400,16 +1406,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.83203125" style="1" customWidth="1"/>
-    <col min="2" max="6" width="25.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.1640625" customWidth="1"/>
+    <col min="1" max="1" width="25.85546875" style="1" customWidth="1"/>
+    <col min="2" max="6" width="25.85546875" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="8.5" customWidth="1"/>
+    <col min="9" max="9" width="8.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" s="1" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1434,7 +1440,7 @@
       <c r="J1"/>
       <c r="K1"/>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" s="1" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>202</v>
       </c>
@@ -1451,7 +1457,7 @@
       <c r="J2"/>
       <c r="K2"/>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1476,7 +1482,7 @@
       <c r="J3"/>
       <c r="K3"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1496,7 +1502,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1516,7 +1522,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1536,7 +1542,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -1556,7 +1562,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -1573,7 +1579,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -1590,7 +1596,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1610,7 +1616,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
@@ -1630,7 +1636,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
@@ -1650,7 +1656,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
@@ -1670,7 +1676,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
@@ -1690,7 +1696,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>39</v>
       </c>
@@ -1710,7 +1716,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>41</v>
       </c>
@@ -1730,7 +1736,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>45</v>
       </c>
@@ -1750,7 +1756,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>48</v>
       </c>
@@ -1770,7 +1776,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>51</v>
       </c>
@@ -1790,7 +1796,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>53</v>
       </c>
@@ -1810,7 +1816,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>55</v>
       </c>
@@ -1830,7 +1836,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>57</v>
       </c>
@@ -1850,7 +1856,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>59</v>
       </c>
@@ -1870,7 +1876,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>62</v>
       </c>
@@ -1890,7 +1896,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>66</v>
       </c>
@@ -1910,7 +1916,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>68</v>
       </c>
@@ -1930,7 +1936,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>69</v>
       </c>
@@ -1950,7 +1956,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>70</v>
       </c>
@@ -1970,7 +1976,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>72</v>
       </c>
@@ -1990,7 +1996,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>74</v>
       </c>
@@ -2010,7 +2016,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>77</v>
       </c>
@@ -2030,7 +2036,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>78</v>
       </c>
@@ -2050,7 +2056,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>79</v>
       </c>
@@ -2070,7 +2076,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>81</v>
       </c>
@@ -2090,7 +2096,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>83</v>
       </c>
@@ -2110,7 +2116,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>86</v>
       </c>
@@ -2130,7 +2136,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>89</v>
       </c>
@@ -2150,7 +2156,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>91</v>
       </c>
@@ -2170,7 +2176,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>193</v>
       </c>
@@ -2190,7 +2196,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>195</v>
       </c>
@@ -2210,7 +2216,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>198</v>
       </c>
@@ -2230,7 +2236,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>200</v>
       </c>
@@ -2250,7 +2256,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>203</v>
       </c>
@@ -2270,7 +2276,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>210</v>
       </c>
@@ -2290,7 +2296,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>211</v>
       </c>
@@ -2310,7 +2316,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>213</v>
       </c>
@@ -2330,7 +2336,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>216</v>
       </c>
@@ -2350,7 +2356,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>218</v>
       </c>
@@ -2370,7 +2376,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>234</v>
       </c>
@@ -2390,19 +2396,36 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A50"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>237</v>
+      </c>
+      <c r="B50" t="s">
+        <v>237</v>
+      </c>
+      <c r="C50" t="s">
+        <v>237</v>
+      </c>
+      <c r="D50" t="s">
+        <v>63</v>
+      </c>
+      <c r="E50" t="s">
+        <v>236</v>
+      </c>
+      <c r="F50" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54"/>
     </row>
   </sheetData>
@@ -2419,12 +2442,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="6" width="25.83203125" customWidth="1"/>
+    <col min="1" max="6" width="25.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" s="1" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2449,7 +2472,7 @@
       <c r="J1"/>
       <c r="K1"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>93</v>
       </c>
@@ -2469,7 +2492,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>95</v>
       </c>
@@ -2489,7 +2512,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>97</v>
       </c>
@@ -2509,7 +2532,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>99</v>
       </c>
@@ -2529,7 +2552,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>101</v>
       </c>
@@ -2549,7 +2572,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>102</v>
       </c>
@@ -2569,7 +2592,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>103</v>
       </c>
@@ -2589,7 +2612,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>104</v>
       </c>
@@ -2609,7 +2632,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>106</v>
       </c>
@@ -2629,7 +2652,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>107</v>
       </c>
@@ -2649,7 +2672,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>109</v>
       </c>
@@ -2669,7 +2692,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>112</v>
       </c>
@@ -2689,7 +2712,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>114</v>
       </c>
@@ -2709,7 +2732,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>116</v>
       </c>
@@ -2729,7 +2752,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>118</v>
       </c>
@@ -2749,7 +2772,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>120</v>
       </c>
@@ -2769,7 +2792,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>121</v>
       </c>
@@ -2789,7 +2812,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>122</v>
       </c>
@@ -2809,7 +2832,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>232</v>
       </c>
@@ -2840,14 +2863,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="6" width="25.83203125" customWidth="1"/>
-    <col min="7" max="7" width="39.1640625" customWidth="1"/>
+    <col min="1" max="6" width="25.85546875" customWidth="1"/>
+    <col min="7" max="7" width="39.140625" customWidth="1"/>
     <col min="8" max="8" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2870,7 +2893,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>124</v>
       </c>
@@ -2890,7 +2913,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>128</v>
       </c>
@@ -2910,7 +2933,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>131</v>
       </c>
@@ -2930,7 +2953,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>134</v>
       </c>
@@ -2950,7 +2973,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>137</v>
       </c>
@@ -2970,7 +2993,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>141</v>
       </c>
@@ -2990,7 +3013,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>144</v>
       </c>
@@ -3010,7 +3033,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>146</v>
       </c>
@@ -3030,7 +3053,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>148</v>
       </c>
@@ -3050,7 +3073,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>150</v>
       </c>
@@ -3070,7 +3093,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>153</v>
       </c>
@@ -3090,7 +3113,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>156</v>
       </c>
@@ -3110,7 +3133,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>159</v>
       </c>
@@ -3130,7 +3153,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>161</v>
       </c>
@@ -3150,7 +3173,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>164</v>
       </c>
@@ -3170,7 +3193,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>166</v>
       </c>
@@ -3190,7 +3213,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>169</v>
       </c>
@@ -3210,7 +3233,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>172</v>
       </c>
@@ -3230,7 +3253,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>174</v>
       </c>
@@ -3250,7 +3273,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>227</v>
       </c>
@@ -3270,7 +3293,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>222</v>
       </c>
@@ -3293,7 +3316,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>225</v>
       </c>
@@ -3313,7 +3336,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>222</v>
       </c>
@@ -3344,12 +3367,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="6" width="25.83203125" customWidth="1"/>
+    <col min="1" max="6" width="25.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" s="1" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3374,7 +3397,7 @@
       <c r="J1"/>
       <c r="K1"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>177</v>
       </c>
@@ -3385,7 +3408,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>180</v>
       </c>
@@ -3396,7 +3419,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>182</v>
       </c>
@@ -3407,7 +3430,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>185</v>
       </c>
@@ -3418,7 +3441,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>187</v>
       </c>
@@ -3429,7 +3452,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>189</v>
       </c>
@@ -3440,7 +3463,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>191</v>
       </c>
@@ -3451,7 +3474,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>207</v>
       </c>
@@ -3462,7 +3485,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>209</v>
       </c>
@@ -3473,7 +3496,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>231</v>
       </c>
